--- a/data/trans_dic/P57_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P57_R-Edad-trans_dic.xlsx
@@ -514,7 +514,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con autopercepción de la felicidad menor o igual a 6 (Likert 0 a 10)</t>
+          <t>Población con autopercepción de la felicidad menor o igual a 6 (Likert 0 a 10) (tasa de respuesta: 99,48%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -632,32 +632,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,99; 8,97</t>
+          <t>3,92; 9,01</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,32; 7,04</t>
+          <t>1,12; 6,94</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,73; 9,66</t>
+          <t>4,71; 9,93</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,98; 12,03</t>
+          <t>4,03; 11,97</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,84; 8,54</t>
+          <t>4,99; 8,54</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,11; 7,48</t>
+          <t>3,08; 7,64</t>
         </is>
       </c>
     </row>
@@ -712,32 +712,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>10,16; 15,89</t>
+          <t>10,26; 16,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,81; 11,98</t>
+          <t>5,17; 11,47</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,59; 13,58</t>
+          <t>8,71; 13,68</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,36; 8,63</t>
+          <t>3,42; 8,52</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,21; 14,18</t>
+          <t>10,26; 14,24</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,75; 9,1</t>
+          <t>4,85; 9,22</t>
         </is>
       </c>
     </row>
@@ -792,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>11,84; 17,49</t>
+          <t>11,95; 17,67</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,97; 10,82</t>
+          <t>5,87; 10,53</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11,31; 16,79</t>
+          <t>11,43; 16,6</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,75; 9,53</t>
+          <t>5,75; 9,61</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>12,42; 16,19</t>
+          <t>12,21; 16,21</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,33; 9,38</t>
+          <t>6,27; 9,33</t>
         </is>
       </c>
     </row>
@@ -872,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>18,88; 25,71</t>
+          <t>18,66; 25,71</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,55; 11,56</t>
+          <t>3,3; 11,51</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18,85; 25,7</t>
+          <t>18,92; 25,94</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11,82; 16,88</t>
+          <t>11,93; 16,78</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>19,61; 24,36</t>
+          <t>19,58; 24,38</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,02; 12,96</t>
+          <t>6,37; 13,12</t>
         </is>
       </c>
     </row>
@@ -952,32 +952,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>15,99; 23,7</t>
+          <t>15,72; 23,69</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>18,17; 24,34</t>
+          <t>18,03; 24,32</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29,7; 37,91</t>
+          <t>29,04; 38,23</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>22,01; 27,75</t>
+          <t>22,35; 28,14</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>23,66; 29,53</t>
+          <t>23,98; 30,14</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,08; 25,3</t>
+          <t>21,05; 25,21</t>
         </is>
       </c>
     </row>
@@ -1032,32 +1032,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>22,9; 32,61</t>
+          <t>22,81; 32,36</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>15,5; 22,08</t>
+          <t>15,53; 22,03</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>33,23; 43,39</t>
+          <t>33,2; 43,3</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6,82; 25,88</t>
+          <t>6,24; 25,91</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>29,4; 36,54</t>
+          <t>29,92; 36,96</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9,58; 22,69</t>
+          <t>9,19; 22,88</t>
         </is>
       </c>
     </row>
@@ -1112,32 +1112,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>35,45; 46,1</t>
+          <t>34,93; 46,39</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>26,81; 35,53</t>
+          <t>26,45; 34,82</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>42,85; 54,52</t>
+          <t>43,58; 54,99</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>31,39; 37,78</t>
+          <t>31,3; 37,79</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>41,41; 49,86</t>
+          <t>41,62; 49,75</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>30,35; 35,61</t>
+          <t>30,37; 35,63</t>
         </is>
       </c>
     </row>
@@ -1192,32 +1192,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>17,16; 19,78</t>
+          <t>17,26; 19,93</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>9,79; 13,88</t>
+          <t>9,62; 13,91</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>22,11; 25,03</t>
+          <t>21,94; 24,87</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12,85; 17,37</t>
+          <t>12,66; 17,32</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>20,07; 22,14</t>
+          <t>20,09; 22,08</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,3; 15,33</t>
+          <t>12,52; 15,33</t>
         </is>
       </c>
     </row>
@@ -1269,7 +1269,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con autopercepción de la felicidad menor o igual a 6 (Likert 0 a 10)</t>
+          <t>Población con autopercepción de la felicidad menor o igual a 6 (Likert 0 a 10) (tasa de respuesta: 99,48%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1425,32 +1425,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>16727; 37616</t>
+          <t>16454; 37802</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5266; 28149</t>
+          <t>4470; 27745</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>18579; 37956</t>
+          <t>18514; 38992</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12451; 37680</t>
+          <t>12608; 37495</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>39325; 69399</t>
+          <t>40535; 69386</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>22204; 53361</t>
+          <t>21980; 54507</t>
         </is>
       </c>
     </row>
@@ -1543,32 +1543,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>59549; 93133</t>
+          <t>60139; 93781</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>20380; 50750</t>
+          <t>21886; 48568</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>48024; 75941</t>
+          <t>48696; 76489</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>17151; 44084</t>
+          <t>17444; 43477</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>116857; 162418</t>
+          <t>117488; 163087</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>44404; 85038</t>
+          <t>45349; 86090</t>
         </is>
       </c>
     </row>
@@ -1661,32 +1661,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>78878; 116527</t>
+          <t>79632; 117710</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>32028; 58025</t>
+          <t>31492; 56486</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>74694; 110877</t>
+          <t>75502; 109631</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>31133; 51618</t>
+          <t>31168; 52085</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>164790; 214761</t>
+          <t>162020; 215042</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>68212; 101074</t>
+          <t>67635; 100602</t>
         </is>
       </c>
     </row>
@@ -1779,32 +1779,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>121359; 165278</t>
+          <t>119955; 165254</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>31558; 102612</t>
+          <t>29261; 102222</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>121720; 165974</t>
+          <t>122195; 167543</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>83539; 119329</t>
+          <t>84359; 118672</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>252703; 313842</t>
+          <t>252288; 314103</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>95969; 206754</t>
+          <t>101628; 209208</t>
         </is>
       </c>
     </row>
@@ -1897,32 +1897,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>76263; 112992</t>
+          <t>74944; 112990</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>101317; 135665</t>
+          <t>100524; 135578</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>147255; 187961</t>
+          <t>143971; 189531</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>119917; 151241</t>
+          <t>121807; 153351</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>230140; 287201</t>
+          <t>233215; 293183</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>232377; 278899</t>
+          <t>232034; 277896</t>
         </is>
       </c>
     </row>
@@ -2015,32 +2015,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>76108; 108382</t>
+          <t>75820; 107569</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>56732; 80798</t>
+          <t>56826; 80636</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>125521; 163895</t>
+          <t>125410; 163582</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>41397; 157151</t>
+          <t>37927; 157374</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>208747; 259483</t>
+          <t>212464; 262436</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>93272; 220867</t>
+          <t>89445; 222699</t>
         </is>
       </c>
     </row>
@@ -2133,32 +2133,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>91108; 118478</t>
+          <t>89763; 119219</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>74654; 98951</t>
+          <t>73664; 96956</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>169882; 216171</t>
+          <t>172781; 218025</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>130404; 156966</t>
+          <t>130056; 157012</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>270623; 325858</t>
+          <t>271981; 325127</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>210595; 247083</t>
+          <t>210757; 247235</t>
         </is>
       </c>
     </row>
@@ -2251,32 +2251,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>580009; 668542</t>
+          <t>583378; 673888</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>337766; 478937</t>
+          <t>331725; 479683</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>780032; 882980</t>
+          <t>774090; 877276</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>467756; 632423</t>
+          <t>460815; 630378</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>1386274; 1529294</t>
+          <t>1388120; 1525323</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>872095; 1086800</t>
+          <t>887320; 1086718</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P57_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P57_R-Edad-trans_dic.xlsx
@@ -599,7 +599,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -619,7 +619,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>5,35%</t>
         </is>
       </c>
     </row>
@@ -632,32 +632,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,92; 9,01</t>
+          <t>3,87; 9,15</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,12; 6,94</t>
+          <t>1,45; 7,36</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,71; 9,93</t>
+          <t>4,84; 9,81</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,03; 11,97</t>
+          <t>4,22; 12,68</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,99; 8,54</t>
+          <t>4,84; 8,33</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,08; 7,64</t>
+          <t>3,39; 8,04</t>
         </is>
       </c>
     </row>
@@ -679,7 +679,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>7,61%</t>
         </is>
       </c>
     </row>
@@ -712,32 +712,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>10,26; 16,0</t>
+          <t>10,73; 16,55</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,17; 11,47</t>
+          <t>5,08; 11,58</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,71; 13,68</t>
+          <t>8,65; 13,77</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,42; 8,52</t>
+          <t>4,89; 9,71</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,26; 14,24</t>
+          <t>10,27; 14,12</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,85; 9,22</t>
+          <t>5,77; 9,75</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,96%</t>
         </is>
       </c>
     </row>
@@ -792,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>11,95; 17,67</t>
+          <t>12,03; 17,41</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,87; 10,53</t>
+          <t>6,21; 11,39</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11,43; 16,6</t>
+          <t>11,46; 16,68</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,75; 9,61</t>
+          <t>5,79; 9,28</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>12,21; 16,21</t>
+          <t>12,22; 16,26</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,27; 9,33</t>
+          <t>6,46; 9,54</t>
         </is>
       </c>
     </row>
@@ -839,7 +839,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>13,12%</t>
         </is>
       </c>
     </row>
@@ -872,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>18,66; 25,71</t>
+          <t>18,66; 25,72</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,3; 11,51</t>
+          <t>8,4; 13,25</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18,92; 25,94</t>
+          <t>19,03; 25,74</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11,93; 16,78</t>
+          <t>13,33; 17,73</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>19,58; 24,38</t>
+          <t>19,71; 24,62</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,37; 13,12</t>
+          <t>11,68; 14,96</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -929,7 +929,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>25,32%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>23,03%</t>
         </is>
       </c>
     </row>
@@ -952,32 +952,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>15,72; 23,69</t>
+          <t>15,93; 23,57</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>18,03; 24,32</t>
+          <t>17,47; 23,91</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29,04; 38,23</t>
+          <t>29,08; 37,87</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>22,35; 28,14</t>
+          <t>22,77; 28,12</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>23,98; 30,14</t>
+          <t>23,88; 29,84</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,05; 25,21</t>
+          <t>20,98; 25,14</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>21,73%</t>
         </is>
       </c>
     </row>
@@ -1032,32 +1032,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>22,81; 32,36</t>
+          <t>22,9; 33,11</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>15,53; 22,03</t>
+          <t>15,29; 21,22</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>33,2; 43,3</t>
+          <t>33,09; 43,07</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6,24; 25,91</t>
+          <t>22,07; 28,15</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>29,92; 36,96</t>
+          <t>29,72; 36,59</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9,19; 22,88</t>
+          <t>19,71; 23,91</t>
         </is>
       </c>
     </row>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>30,43%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>34,37%</t>
+          <t>34,49%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>32,97%</t>
+          <t>32,85%</t>
         </is>
       </c>
     </row>
@@ -1112,32 +1112,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>34,93; 46,39</t>
+          <t>35,07; 46,26</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>26,45; 34,82</t>
+          <t>26,09; 34,24</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>43,58; 54,99</t>
+          <t>42,74; 54,41</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>31,3; 37,79</t>
+          <t>31,28; 37,69</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>41,62; 49,75</t>
+          <t>41,55; 49,98</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>30,37; 35,63</t>
+          <t>30,23; 35,49</t>
         </is>
       </c>
     </row>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1179,7 +1179,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>15,4%</t>
         </is>
       </c>
     </row>
@@ -1192,22 +1192,22 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>17,26; 19,93</t>
+          <t>17,29; 20,1</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>9,62; 13,91</t>
+          <t>12,23; 14,61</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>21,94; 24,87</t>
+          <t>22,03; 24,96</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12,66; 17,32</t>
+          <t>16,15; 18,26</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,52; 15,33</t>
+          <t>14,67; 16,23</t>
         </is>
       </c>
     </row>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12926</t>
+          <t>13895</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21753</t>
+          <t>27283</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>34678</t>
+          <t>41178</t>
         </is>
       </c>
     </row>
@@ -1425,32 +1425,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>16454; 37802</t>
+          <t>16224; 38376</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4470; 27745</t>
+          <t>5914; 30018</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>18514; 38992</t>
+          <t>19023; 38534</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12608; 37495</t>
+          <t>15302; 45957</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>40535; 69386</t>
+          <t>39307; 67636</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>21980; 54507</t>
+          <t>26125; 61930</t>
         </is>
       </c>
     </row>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>33559</t>
+          <t>38858</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>29730</t>
+          <t>35483</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>63289</t>
+          <t>74341</t>
         </is>
       </c>
     </row>
@@ -1543,32 +1543,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>60139; 93781</t>
+          <t>62850; 96954</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>21886; 48568</t>
+          <t>24212; 55208</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>48696; 76489</t>
+          <t>48356; 76989</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>17444; 43477</t>
+          <t>24474; 48541</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>117488; 163087</t>
+          <t>117649; 161674</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>45349; 86090</t>
+          <t>56392; 95281</t>
         </is>
       </c>
     </row>
@@ -1628,7 +1628,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>43035</t>
+          <t>52566</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1638,7 +1638,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>40113</t>
+          <t>46362</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1648,7 +1648,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>83148</t>
+          <t>98928</t>
         </is>
       </c>
     </row>
@@ -1661,32 +1661,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>79632; 117710</t>
+          <t>80150; 116009</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>31492; 56486</t>
+          <t>38531; 70702</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>75502; 109631</t>
+          <t>75679; 110142</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>31168; 52085</t>
+          <t>35948; 57681</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>162020; 215042</t>
+          <t>162147; 215788</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>67635; 100602</t>
+          <t>80184; 118454</t>
         </is>
       </c>
     </row>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>67877</t>
+          <t>74125</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>102520</t>
+          <t>113717</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>170396</t>
+          <t>187842</t>
         </is>
       </c>
     </row>
@@ -1779,32 +1779,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>119955; 165254</t>
+          <t>119937; 165312</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>29261; 102222</t>
+          <t>58836; 92865</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>122195; 167543</t>
+          <t>122898; 166230</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>84359; 118672</t>
+          <t>97497; 129695</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>252288; 314103</t>
+          <t>253918; 317268</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>101628; 209208</t>
+          <t>167259; 214258</t>
         </is>
       </c>
     </row>
@@ -1864,7 +1864,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>117833</t>
+          <t>125528</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>136337</t>
+          <t>153353</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1884,7 +1884,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>254169</t>
+          <t>278881</t>
         </is>
       </c>
     </row>
@@ -1897,32 +1897,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>74944; 112990</t>
+          <t>75953; 112397</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>100524; 135578</t>
+          <t>105753; 144701</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>143971; 189531</t>
+          <t>144198; 187766</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>121807; 153351</t>
+          <t>137941; 170321</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>233215; 293183</t>
+          <t>232242; 290195</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>232034; 277896</t>
+          <t>254095; 304411</t>
         </is>
       </c>
     </row>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>68661</t>
+          <t>73833</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>100624</t>
+          <t>109333</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2002,7 +2002,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>169284</t>
+          <t>183167</t>
         </is>
       </c>
     </row>
@@ -2015,32 +2015,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>75820; 107569</t>
+          <t>76107; 110044</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>56826; 80636</t>
+          <t>61910; 85911</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>125410; 163582</t>
+          <t>125014; 162686</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>37927; 157374</t>
+          <t>96680; 123308</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>212464; 262436</t>
+          <t>211031; 259866</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>89445; 222699</t>
+          <t>166155; 201526</t>
         </is>
       </c>
     </row>
@@ -2100,7 +2100,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>85986</t>
+          <t>93002</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -2110,7 +2110,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>142774</t>
+          <t>156425</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>228761</t>
+          <t>249427</t>
         </is>
       </c>
     </row>
@@ -2133,32 +2133,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>89763; 119219</t>
+          <t>90132; 118888</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>73664; 96956</t>
+          <t>79736; 104663</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>172781; 218025</t>
+          <t>169467; 215724</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>130056; 157012</t>
+          <t>141882; 170957</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>271981; 325127</t>
+          <t>271548; 326617</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>210757; 247235</t>
+          <t>229482; 269404</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>429876</t>
+          <t>471807</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -2228,7 +2228,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>573850</t>
+          <t>641958</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -2238,7 +2238,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1003726</t>
+          <t>1113764</t>
         </is>
       </c>
     </row>
@@ -2251,32 +2251,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>583378; 673888</t>
+          <t>584516; 679576</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>331725; 479683</t>
+          <t>430826; 514378</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>774090; 877276</t>
+          <t>777164; 880662</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>460815; 630378</t>
+          <t>599754; 677803</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>1388120; 1525323</t>
+          <t>1388057; 1525720</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>887320; 1086718</t>
+          <t>1061579; 1174508</t>
         </is>
       </c>
     </row>
